--- a/design/tables/ArtAtlas.xlsx
+++ b/design/tables/ArtAtlas.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtAtlas" sheetId="1" r:id="Re0666288646941c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtAtlas" sheetId="1" r:id="R33230a01f9a84327"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -494,6 +494,23 @@
         <x:v>512</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>staffEvolution</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>gameplay/towers/atlas_staff_evolution/texture</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ArtAtlas.xlsx
+++ b/design/tables/ArtAtlas.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtAtlas" sheetId="1" r:id="R33230a01f9a84327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtAtlas" sheetId="1" r:id="Rb552151af65a46b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +32,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +60,11 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -57,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -80,6 +95,32 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -375,140 +416,157 @@
         <x:v>height</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A6" s="7" t="n">
+    <x:row r="6" ht="48" hidden="0" customHeight="1">
+      <x:c r="A6" s="17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="str">
+      <x:c r="B6" s="15" t="str">
         <x:v>staff</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="15" t="str">
         <x:v>gameplay/towers/atlas_staff_idle/texture</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E6" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A7" s="7" t="n">
+      <x:c r="D6" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E6" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
+      <x:c r="A7" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="str">
+      <x:c r="B7" s="15" t="str">
         <x:v>props</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="15" t="str">
         <x:v>gameplay/maps/atlas_battle_props/texture</x:v>
       </x:c>
-      <x:c r="D7" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E7" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A8" s="7" t="n">
+      <x:c r="D7" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" hidden="0" customHeight="1">
+      <x:c r="A8" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="2" t="str">
+      <x:c r="B8" s="15" t="str">
         <x:v>enemies</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="15" t="str">
         <x:v>gameplay/enemies/atlas_enemies/texture</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E8" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A9" s="7" t="n">
+      <x:c r="D8" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E8" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="48" hidden="0" customHeight="1">
+      <x:c r="A9" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="2" t="str">
+      <x:c r="B9" s="15" t="str">
         <x:v>scenery</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="15" t="str">
         <x:v>gameplay/maps/atlas_battle_scenery/texture</x:v>
       </x:c>
-      <x:c r="D9" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E9" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="7" t="n">
+      <x:c r="D9" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E9" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="48" hidden="0" customHeight="1">
+      <x:c r="A10" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="2" t="str">
+      <x:c r="B10" s="15" t="str">
         <x:v>ui</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="C10" s="15" t="str">
         <x:v>ui/icons/atlas_battle_ui/texture</x:v>
       </x:c>
-      <x:c r="D10" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E10" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A11" s="7" t="n">
+      <x:c r="D10" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="48" hidden="0" customHeight="1">
+      <x:c r="A11" s="17" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="2" t="str">
+      <x:c r="B11" s="15" t="str">
         <x:v>staffNew</x:v>
       </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="C11" s="15" t="str">
         <x:v>gameplay/towers/atlas_staff_expansion/texture</x:v>
       </x:c>
-      <x:c r="D11" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E11" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A12" s="7" t="n">
+      <x:c r="D11" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" hidden="0" customHeight="1">
+      <x:c r="A12" s="17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="2" t="str">
+      <x:c r="B12" s="15" t="str">
         <x:v>enemiesNew</x:v>
       </x:c>
-      <x:c r="C12" s="8" t="str">
+      <x:c r="C12" s="15" t="str">
         <x:v>gameplay/enemies/atlas_campaign_enemies/texture</x:v>
       </x:c>
-      <x:c r="D12" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="E12" s="7" t="n">
-        <x:v>512</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="n">
+      <x:c r="D12" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B13" s="18" t="str">
         <x:v>staffEvolution</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C13" s="18" t="str">
         <x:v>gameplay/towers/atlas_staff_evolution/texture</x:v>
       </x:c>
-      <x:c r="D13" t="n">
+      <x:c r="D13" s="18" t="n">
         <x:v>1024</x:v>
       </x:c>
-      <x:c r="E13" t="n">
-        <x:v>512</x:v>
+      <x:c r="E13" s="18" t="n">
+        <x:v>512</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="18" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="str">
+        <x:v>staffEvolutionExpansion</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>gameplay/towers/atlas_staff_evolution_expansion/texture</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="n">
+        <x:v>1024</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/ArtAtlas.xlsx
+++ b/design/tables/ArtAtlas.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtAtlas" sheetId="1" r:id="Rb552151af65a46b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArtAtlas" sheetId="1" r:id="R26a51bf6f53b4884"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -569,6 +569,23 @@
         <x:v>1024</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>challengePerks</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>ui/icons/atlas_challenge_perks/texture</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>2048</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
